--- a/成果物/松藤華奈様_コミッション計算_FY26.xlsx
+++ b/成果物/松藤華奈様_コミッション計算_FY26.xlsx
@@ -1372,7 +1372,7 @@
         <v/>
       </c>
       <c r="I14" s="52">
-        <f>ROUNDDOWN(I5*(1-$B$29)*$B$25,0)</f>
+        <f>ROUNDDOWN(I5*(1-$B$29)*0.6,0)</f>
         <v/>
       </c>
       <c r="J14" s="52">
@@ -1435,7 +1435,7 @@
         <v/>
       </c>
       <c r="I15" s="52">
-        <f>ROUNDDOWN(I6*(1-$B$29)*$B$26,0)</f>
+        <f>ROUNDDOWN(I6*(1-$B$29)*0.4,0)</f>
         <v/>
       </c>
       <c r="J15" s="52">
@@ -1498,7 +1498,7 @@
         <v/>
       </c>
       <c r="I16" s="52">
-        <f>ROUNDDOWN(I7*(1-$B$29)*$B$27,0)</f>
+        <f>ROUNDDOWN(I7*(1-$B$29)*0.5,0)</f>
         <v/>
       </c>
       <c r="J16" s="52">
@@ -1561,7 +1561,7 @@
         <v/>
       </c>
       <c r="I17" s="52">
-        <f>ROUNDDOWN(I8*$B$28,0)</f>
+        <f>ROUNDDOWN(I8*0.05,0)</f>
         <v/>
       </c>
       <c r="J17" s="52">
@@ -1624,7 +1624,7 @@
         <v/>
       </c>
       <c r="I18" s="52">
-        <f>ROUNDDOWN(I9*$B$28,0)</f>
+        <f>ROUNDDOWN(I9*0.05,0)</f>
         <v/>
       </c>
       <c r="J18" s="52">
@@ -1685,9 +1685,8 @@
       <c r="H19" s="52" t="n">
         <v>0</v>
       </c>
-      <c r="I19" s="52">
-        <f>(I11*2)*I10</f>
-        <v/>
+      <c r="I19" s="52" t="n">
+        <v>0</v>
       </c>
       <c r="J19" s="52">
         <f>(J11*2)*J10</f>
@@ -4672,7 +4671,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:E17"/>
+  <dimension ref="A1:E18"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.66796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="26" customWidth="1" style="39" min="1" max="1"/>
@@ -4721,14 +4720,15 @@
           <t>ご自身の顧客売上</t>
         </is>
       </c>
-      <c r="B4" s="67" t="n"/>
+      <c r="B4" s="67" t="n">
+        <v>0</v>
+      </c>
       <c r="C4" s="68">
         <f>B4*(1-年間サマリー!$B$29)</f>
         <v/>
       </c>
-      <c r="D4" s="69">
-        <f>年間サマリー!$B$25</f>
-        <v/>
+      <c r="D4" s="69" t="n">
+        <v>0.6</v>
       </c>
       <c r="E4" s="52">
         <f>ROUNDDOWN(C4*D4,0)</f>
@@ -4741,14 +4741,15 @@
           <t>施術売上（指名なし）</t>
         </is>
       </c>
-      <c r="B5" s="70" t="n"/>
+      <c r="B5" s="70" t="n">
+        <v>485880</v>
+      </c>
       <c r="C5" s="68">
         <f>B5*(1-年間サマリー!$B$29)</f>
         <v/>
       </c>
-      <c r="D5" s="69">
-        <f>年間サマリー!$B$26</f>
-        <v/>
+      <c r="D5" s="69" t="n">
+        <v>0.4</v>
       </c>
       <c r="E5" s="52">
         <f>ROUNDDOWN(C5*D5,0)</f>
@@ -4761,14 +4762,15 @@
           <t>指名売上</t>
         </is>
       </c>
-      <c r="B6" s="70" t="n"/>
+      <c r="B6" s="70" t="n">
+        <v>20280</v>
+      </c>
       <c r="C6" s="68">
         <f>B6*(1-年間サマリー!$B$29)</f>
         <v/>
       </c>
-      <c r="D6" s="69">
-        <f>年間サマリー!$B$27</f>
-        <v/>
+      <c r="D6" s="69" t="n">
+        <v>0.5</v>
       </c>
       <c r="E6" s="52">
         <f>ROUNDDOWN(C6*D6,0)</f>
@@ -4781,14 +4783,15 @@
           <t>店販売上</t>
         </is>
       </c>
-      <c r="B7" s="70" t="n"/>
+      <c r="B7" s="70" t="n">
+        <v>4400</v>
+      </c>
       <c r="C7" s="68">
         <f>B7</f>
         <v/>
       </c>
-      <c r="D7" s="69">
-        <f>年間サマリー!$B$28</f>
-        <v/>
+      <c r="D7" s="69" t="n">
+        <v>0.05</v>
       </c>
       <c r="E7" s="52">
         <f>ROUNDDOWN(B7*D7,0)</f>
@@ -4801,14 +4804,15 @@
           <t>オプション売上</t>
         </is>
       </c>
-      <c r="B8" s="70" t="n"/>
+      <c r="B8" s="70" t="n">
+        <v>22100</v>
+      </c>
       <c r="C8" s="68">
         <f>B8</f>
         <v/>
       </c>
-      <c r="D8" s="69">
-        <f>年間サマリー!$B$28</f>
-        <v/>
+      <c r="D8" s="69" t="n">
+        <v>0.05</v>
       </c>
       <c r="E8" s="52">
         <f>ROUNDDOWN(B8*D8,0)</f>
@@ -4831,7 +4835,9 @@
           <t>勤務日数</t>
         </is>
       </c>
-      <c r="B11" s="71" t="n"/>
+      <c r="B11" s="71" t="n">
+        <v>17</v>
+      </c>
       <c r="C11" s="72" t="n"/>
       <c r="D11" s="72" t="n"/>
       <c r="E11" s="72" t="n"/>
@@ -4858,9 +4864,8 @@
       <c r="B13" s="72" t="n"/>
       <c r="C13" s="72" t="n"/>
       <c r="D13" s="72" t="n"/>
-      <c r="E13" s="52">
-        <f>B12*2*B11</f>
-        <v/>
+      <c r="E13" s="52" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="14" ht="15" customHeight="1" s="40"/>
@@ -4885,6 +4890,13 @@
       <c r="A17" s="42" t="inlineStr">
         <is>
           <t>※ 青セル=入力欄、グレーセル=自動計算、料率は年間サマリーで一元管理</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>※7月〜新料率(自己60/指名なし40/指名50/店販オプ5%・交通費なし)。指名料除外。8月フジイ来店なし。</t>
         </is>
       </c>
     </row>
